--- a/output/北塩原村_村資料点検_20261010.xlsx
+++ b/output/北塩原村_村資料点検_20261010.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_協議会の意見・提案" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_アンケート自由記述の対応状況" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_正本の修正案" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_村への照会" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06b_正本に入れる文章" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_村への照会" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +55,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +87,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -146,6 +152,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -514,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -675,15 +684,32 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>すでに正本に入れたもの</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>最優先の追記5件（V-1 成年後見の計画を位置づけの表に追加／V-2 計画の期間に成年後見の5年間を追加／V-3 障がい者計画の中間見直しの明記／V-4 策定体制に4町村広域の協議会・村議会への説明・公表を追加／V-5 第6章の冒頭に根拠法と計画期間）は、村の方針に明記があり回答を待たずに書けるため、令和8年10月10日に正本へ入れた</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>06b・06シートの状態欄</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>計画策定方針との照合9件／スケジュールの照合10件／進捗管理評価シート7施策／協議会の意見・提案21件／アンケート自由記述14件／正本の修正案26件（追記20・要確認6）／村への照会9件</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>計画策定方針との照合9件／スケジュールの照合10件／進捗管理評価シート7施策／協議会の意見・提案21件／アンケート自由記述14件／正本の修正案26件（追記20・要確認6。うち5件は反映済み）／村への照会9件</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3311,15 +3337,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3367,6 +3394,11 @@
           <t>重さ</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -3399,6 +3431,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>反映済み（令和8年10月10日）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -3431,6 +3468,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>反映済み（令和8年10月10日）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -3463,6 +3505,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>反映済み（令和8年10月10日）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -3495,6 +3542,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>反映済み（令和8年10月10日）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -3527,6 +3579,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>反映済み（令和8年10月10日）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -3559,6 +3616,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -3591,6 +3653,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -3623,6 +3690,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -3655,6 +3727,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -3687,6 +3764,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -3719,6 +3801,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -3751,6 +3838,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -3783,6 +3875,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -3815,6 +3912,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -3847,6 +3949,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3879,6 +3986,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
@@ -3911,6 +4023,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -3943,6 +4060,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -3975,6 +4097,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -4007,6 +4134,11 @@
           <t>中</t>
         </is>
       </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -4039,6 +4171,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -4071,6 +4208,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
@@ -4103,6 +4245,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -4135,6 +4282,11 @@
           <t>最優先</t>
         </is>
       </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -4167,6 +4319,11 @@
           <t>高</t>
         </is>
       </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
@@ -4197,6 +4354,251 @@
       <c r="F31" s="10" t="inlineStr">
         <is>
           <t>高</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>未反映</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>正本に入れる文章（最優先の追記5件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>村の計画策定方針に明記があり、村の回答を待たずに書けるものだけを置いた。build_kitashiobara_honpon.py がこの一覧から読み込んで正本に入れるため、文章の出所はここだけである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>番号</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>入れる先</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>挿入位置</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>根拠（村資料）</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>入れる文章</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>V-1</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>計画の表</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>第1章2 計画の位置づけ（計画名／項目／内容の表）</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>計画名</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>計画策定方針 3（2）③。成年後見制度の利用促進に関する法律第14条第1項</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>［表の行］成年後見制度の利用の
+促進に関する施策に
+ついての基本的な計画 ／ 根拠法令 ／ 成年後見制度の利用促進に関する法律第14条第１項
+［表の行］策定内容 ／ 地域の実情に応じた成年後見制度の利用の促進に関する施策を定める（計画期間：令和９年度～令和13年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>V-2</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>年度表</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>第1章3 計画の期間（年度表と本文）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>なお、いずれの計画も計画期間中において、社会情勢の変化や国の方針変更等に伴い、計画の見直しが必要と判断された場合は、見直しを行います。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>計画策定方針 2・3（2）③</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>また、本計画には、成年後見制度の利用促進に関する法律第14条第１項に基づく「成年後見制度の利用の促進に関する施策についての基本的な計画」を内包します。同計画の計画期間は、令和９年度から令和13年度までの５年間とし、障がい福祉計画及び障がい児福祉計画の計画期間（３年間）とは異なります。
+［表の行］成年後見
+利用促進計画 ／ ― ／ 本計画に内包（５年間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>V-3</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>第1章2 計画の位置づけ（末尾。移植17の前）</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>また、北塩原村第五次総合振興計画の施策体系においては、政策分野「福祉」の中の「生活弱者」に位置づけられる施策19「穏やかな暮らしの支援」として、「障がい者福祉制度の運営、適切な生活保障」が掲げられており、本計画はこの施策を具体化する分野別計画として位置づけられます。本計画期間中に策定される次期総合振興計画についても、その内容との整合を図ります。</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>計画策定方針 3（1）</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>なお、第４次北塩原村障がい者計画（令和６年度～令和11年度）は、本計画の策定にあわせて中間見直しを行います。中間見直しでは、第３章に掲げる基本施策ごとの目標値について達成状況を確認し、目標値を改める場合は同章に改定後の値を掲げます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>V-4</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>項</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>第1章5 計画策定の体制（（5）〜（7）として追加）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>本計画案を、令和９年２月８日～令和９年２月22日まで村ホームページ等で公開し、広く村民の方々から意見を募りました。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>計画策定方針 7（4）（6）（7）</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>【（５）４町村広域の障がい者自立支援協議会の開催】猪苗代町、磐梯町、湯川村及び本村の４町村で構成する広域の障がい者自立支援協議会においても、保健・福祉の関係者、障がい当事者、教育関係者、障がい福祉サービス事業者等の委員の意見を聴取しながら検討しました。本村単独では確保が難しいサービスの広域的な利用や、地域生活支援拠点の共同整備については、この場で協議します。
+【（６）村議会への説明】議会全員協議会において、計画案について説明しました。
+【（７）計画の公表】策定した計画は、関係機関へ送付するとともに、村のホームページに掲載して公表します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>V-5</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>第6章 成年後見制度の利用促進（章の冒頭）</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>第６章　成年後見制度の利用促進</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>計画策定方針 2・3（2）③</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>本章は、成年後見制度の利用促進に関する法律第14条第１項に基づく「成年後見制度の利用の促進に関する施策についての基本的な計画」として定めるものです。同項は、市町村が国の成年後見制度利用促進基本計画を勘案して、その区域における成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとしています。
+本章の計画期間は、令和９年度から令和13年度までの５年間とします。障がい福祉計画及び障がい児福祉計画の計画期間（令和９年度から令和11年度まで）とは異なるため、次期計画の策定時には、本章の進捗状況を確認したうえで、残る期間の取組みを引き継ぎます。</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4510,7 +4912,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>※ 出所: source/村資料_自立支援協議会_20260525/（令和8年5月25日 協議会資料）</t>
         </is>

--- a/output/北塩原村_村資料点検_20261010.xlsx
+++ b/output/北塩原村_村資料点検_20261010.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>計画策定方針との照合9件／スケジュールの照合10件／進捗管理評価シート7施策／協議会の意見・提案21件／アンケート自由記述14件／正本の修正案26件（追記20・要確認6。うち5件は反映済み）／村への照会9件</t>
+          <t>計画策定方針との照合9件／スケジュールの照合10件／進捗管理評価シート7施策／協議会の意見・提案21件／アンケート自由記述14件／正本の修正案26件（追記19・要確認7。うち5件は反映済み）／村への照会9件</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -992,22 +992,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>第1章4（2）主な見直し事項に記載。高次脳機能障がい9件・住宅セーフティネット2件・虐待・災害は移植6・7で入っている</t>
+          <t>第1章4（2）主な見直し事項に①から⑯まで16項目が村の方針と同じ並びで載っている</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>⑬地域差の是正・指定の在り方と⑮スポーツ・健康増進活動が明示されていない</t>
+          <t>項目の数と並びは一致している。違いは⑬で、村の方針が「地域差の是正・指定の在り方等」と指定の在り方まで含めているのに対し、正本は「地域差の是正等」とし、内容を重度障がい者の利用者数の見込みの設定に絞っている</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>第1章4（2）に村の方針が挙げる16項目との対応を示す（村の資料と同じ並びにすると庁議・協議会で照合しやすい）</t>
+          <t>⑬に指定の在り方（県が行う事業者の指定と地域のニーズのずれ）を加えるかを村と相談する。16項目の網羅は直す必要がない</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
     </row>
@@ -3653,9 +3653,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>未反映</t>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>W-2として反映済み（令和8年10月10日）</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>法定雇用率の段階的引上げ（令和8年7月から地方公共団体3.0％）を踏まえた継続的・安定的な雇用確保が課題であること、優先調達の取扱い物品が食料品や日用雑貨中心で発注調整が困難であることを書く</t>
+          <t>法定雇用率の引上げ（令和8年7月から民間企業2.7％・国及び地方公共団体3.0％）は第1章4（3）に既にある。足すのは村の課題の側で、事業主への直接的な働きかけに至っていないこと、優先調達の取扱い物品が食料品や日用雑貨中心で発注調整が困難であること、継続的な発注の仕組みづくりが課題であることを書く</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>村の策定方針が挙げる16項目との対応を示す（村の資料と同じ並びにすると協議会・庁議で照合しやすい）</t>
+          <t>16項目は村の方針と同じ並びで載っており、網羅に漏れはない。⑬について、村の方針は「地域差の是正・指定の在り方等」と指定の在り方まで含めているため、県が行う事業者の指定と地域のニーズのずれに触れるかを相談する</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -4124,14 +4124,14 @@
           <t>計画策定方針 3（4）</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>追記</t>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">

--- a/output/北塩原村_村資料点検_20261010.xlsx
+++ b/output/北塩原村_村資料点検_20261010.xlsx
@@ -3616,9 +3616,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>未反映</t>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>X-1として反映済み（令和8年10月10日）</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_村資料点検_20261010.xlsx
+++ b/output/北塩原村_村資料点検_20261010.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>02シート。照会M-40</t>
+          <t>02シート。照会Ｍ-40</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>01シート。修正案V-3。照会M-44</t>
+          <t>01シート。修正案V-3。照会Ｍ-44</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>修正案V-21〜V-24。照会M-41〜M-43</t>
+          <t>修正案V-21〜V-24。照会Ｍ-41〜Ｍ-43</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>見込量の第1次概算は作成済み。実績集計は村の回答待ち（M-19）</t>
+          <t>見込量の第1次概算は作成済み。実績集計は村の回答待ち（Ｍ-19）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>M-19の回答を最優先で取る（着手順1）</t>
+          <t>Ｍ-19の回答を最優先で取る（着手順1）</t>
         </is>
       </c>
     </row>
@@ -4630,14 +4630,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>この点検で新たに生じた村への照会（M-40〜M-48）</t>
+          <t>この点検で新たに生じた村への照会（Ｍ-40〜Ｍ-48）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の照会はM-39まで。M-40（工程の確認）は、ほかのどの照会よりも先に出す必要がある。</t>
+          <t>既存の照会はＭ-39まで。Ｍ-40（工程の確認）は、ほかのどの照会よりも先に出す必要がある。</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>M-40</t>
+          <t>Ｍ-40</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -4698,7 +4698,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>M-41</t>
+          <t>Ｍ-41</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4725,7 +4725,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>M-42</t>
+          <t>Ｍ-42</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>M-43</t>
+          <t>Ｍ-43</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -4779,7 +4779,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>M-44</t>
+          <t>Ｍ-44</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>M-45</t>
+          <t>Ｍ-45</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>M-46</t>
+          <t>Ｍ-46</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>M-47</t>
+          <t>Ｍ-47</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>M-48</t>
+          <t>Ｍ-48</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">

--- a/output/北塩原村_村資料点検_20261010.xlsx
+++ b/output/北塩原村_村資料点検_20261010.xlsx
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>最優先。会議資料（現行計画の評価・素案・概要版）は作成済みであり、アンケート結果だけが欠ける。アンケートが間に合わない場合の議題の組み替えを村に相談する</t>
+          <t>令和8年10月14日に決着。第2回は11月開催となり、工程は案Ａへ引き直した（kitashiobara_koutei.py）。会議資料（現行計画の評価・素案・概要版）は作成済みであり、アンケート結果は10月に集計・分析する</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>村の決定を確認したうえで、正本 第1章5（4）の日程を直す。前回（第7期）のパブリックコメントは令和6年2月実施で意見0件であり、11月に前倒しするなら周知の方法を変える必要がある</t>
+          <t>令和8年10月14日に決着。パブリックコメントは案Ａにより令和9年1月26日〜2月9日（15日間）とし、正本 第1章5（4）の日程を書き換えた（ＴＫ-4）。11月実施は、策定委員会（第2回）が11月となったため成り立たない。前回（令和6年2月）は意見0件であったため周知の方法も見直す。この日程は村の了解を要する（Ｍ-125）</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>第1章5に4町村広域の協議会を加える。仕様書の「協議会の開催は1回程度」との関係を村と整理する</t>
+          <t>第1章5（5）に4町村広域の協議会を加えた（V-4）。令和8年10月14日に、工程表にも12月の工程として入れた（方針資料・策定委員会資料はいずれも注記に落としていた）。仕様書の「協議会の開催は1回程度」との関係を村と整理する</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>庁議資料（概要版）は作成済み。工程表を方針に合わせる</t>
+          <t>令和8年10月14日に決着。案Ａでは1月中旬に自立支援協議会（計画案の審議）を置き、庁議（計画の決定）は2月19日とした。庁議を1月に置くと、パブリックコメントの前に決定することになる。庁議資料（概要版）は作成済み</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>第1章5に村議会への説明を加え、工程表に議会全員協議会を入れる</t>
+          <t>第1章5（6）に村議会への説明を加えた（V-4）。令和8年10月14日に、工程表にも議会全員協議会を入れた。ただし案Ａでは計画の決定（庁議2月19日）の後の2月下旬に置く。方針の順（議会説明2月・計画決定3月）では未決定の案を議会に説明することになる（Ｍ-125）</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>公表（関係機関への送付・ホームページ掲載）を第1章5に加える</t>
+          <t>公表（関係機関への送付・ホームページ掲載）を第1章5（7）に加えた（V-4）。案Ａでは初校2月26日・再校3月5日・校了3月12日・入稿3月17日・印刷3月19日・製本3月26日・納品3月31日である</t>
         </is>
       </c>
     </row>
@@ -4282,9 +4282,9 @@
           <t>最優先</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>未反映</t>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>ＴＫ-4として反映済み（令和8年10月14日。工程は案Ａ。令和9年1月26日〜2月9日）</t>
         </is>
       </c>
     </row>
@@ -4319,9 +4319,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>未反映</t>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>ＴＫ-2・ＴＫ-3として反映済み（令和8年10月14日。体系は案Ｃ。章名を改め第3章4に表３-３を置いた）</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>【（５）４町村広域の障がい者自立支援協議会の開催】猪苗代町、磐梯町、湯川村及び本村の４町村で構成する広域の障がい者自立支援協議会においても、保健・福祉の関係者、障がい当事者、教育関係者、障がい福祉サービス事業者等の委員の意見を聴取しながら検討しました。本村単独では確保が難しいサービスの広域的な利用や、地域生活支援拠点の共同整備については、この場で協議します。
-【（６）村議会への説明】議会全員協議会において、計画案について説明しました。
+【（６）村議会への説明】議会全員協議会において、決定した計画の内容と令和９年度の主要事業について説明しました。
 【（７）計画の公表】策定した計画は、関係機関へ送付するとともに、村のホームページに掲載して公表します。</t>
         </is>
       </c>

--- a/output/北塩原村_村資料点検_20261010.xlsx
+++ b/output/北塩原村_村資料点検_20261010.xlsx
@@ -4730,12 +4730,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>個別避難計画の現状値</t>
+          <t>個別避難計画の令和7年度の現在値</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>進捗管理評価シートは令和7年度まで1件、協議会での回答は「実質0件」である。①第3章3に載せる現状値はどちらか ②要支援者名簿登載者28名の内訳（障がいのある方の人数） ③令和9〜11年度の策定の目標件数</t>
+          <t>基準値（令和5年度1件）は第4次北塩原村障がい者計画が目標値の表に記しており決着しているため、重ねてお尋ねしない。①進捗管理評価シートの令和7年度まで1件と、協議会での回答「実質0件」との違いの読み方（作成に着手した件数と、本人の同意を得て完成した件数の別か） ②要支援者名簿登載者28名の内訳（障がいのある方の人数） ③令和9〜11年度の策定の目標件数</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
